--- a/Daily Assessment March 13/testdata/excel1.xlsx
+++ b/Daily Assessment March 13/testdata/excel1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Playwright\tests\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assessment\Daily Assessment March 13\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753141DB-464F-47B7-BE6B-9EDE76231F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD68A21B-0951-4592-BAFE-0984E3C50EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -461,10 +461,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,14 +495,14 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>28</v>
+      </c>
       <c r="L1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -533,14 +533,14 @@
       <c r="J2" t="s">
         <v>16</v>
       </c>
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
       <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -571,10 +571,10 @@
       <c r="J3" t="s">
         <v>24</v>
       </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
       <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
         <v>33</v>
       </c>
     </row>
